--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>YUV&amp;MAYU שיר שלי בשבילך</v>
+        <v>אפרת גוש – סוף סוף אושר</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-08</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/yuvmayu-%d7%a9%d7%99%d7%a8-%d7%a9%d7%9c%d7%99-%d7%91%d7%a9%d7%91%d7%99%d7%9c%d7%9a/</v>
+        <v>https://yosmusic.com/%d7%90%d7%a4%d7%a8%d7%aa-%d7%92%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a1%d7%95%d7%a3-%d7%90%d7%95%d7%a9%d7%a8/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-08</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר הוא בלדה רכה ואינטימית שנכתבה ומבוצעת על ידי מאיה לוי ויובל גז, .צמד יוצרות צעירות שנפגשו בלימודיהן בבית הספר למוזיקה רימון. הבלדה מבטאת כמיהה נאיבית-עדינה לאהבה, ומציירת מצב רגשי של המתנה למפגש עם אדם שעדיין לא נכנס לחיים –</v>
+        <v>השיר שייך לשלב בוגר ביצירתה של אפרת גוש, אך הוא מסופר מנקודת מבט צעירה מאוד – כמעט וידויית. בקליפ, הזמרת צופה בדמות שמגלמת אותה כצעירה בת 19, מה שיוצר דיאלוג בין עבר להווה: האישה הבוגרת מתבוננת על החלומות, הפחדים והשאיפות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>YUV&amp;MAYU שיר שלי בשבילך</v>
+        <v>אפרת גוש – סוף סוף אושר</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אפרת גוש – סוף סוף אושר</v>
+        <v>נתנאל ששון – זה רשמי</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%a4%d7%a8%d7%aa-%d7%92%d7%95%d7%a9-%d7%a1%d7%95%d7%a3-%d7%a1%d7%95%d7%a3-%d7%90%d7%95%d7%a9%d7%a8/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%a0%d7%90%d7%9c-%d7%a9%d7%a9%d7%95%d7%9f-%d7%96%d7%94-%d7%a8%d7%a9%d7%9e%d7%99/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-08</v>
+        <v>2026-03-09</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר שייך לשלב בוגר ביצירתה של אפרת גוש, אך הוא מסופר מנקודת מבט צעירה מאוד – כמעט וידויית. בקליפ, הזמרת צופה בדמות שמגלמת אותה כצעירה בת 19, מה שיוצר דיאלוג בין עבר להווה: האישה הבוגרת מתבוננת על החלומות, הפחדים והשאיפות</v>
+        <v>נתנאל ששון שר בלדה ים-תיכונית טיפוסית על אהבה שנגמרה, שמנסה לשלב בין הצהרה של התגברות לבין רגש שלא באמת נעלם. כבר משם השיר ברור שהדובר מבקש להכריז על סיום סופי,  אבל ככל שמתקדמים בטקסט ובביצוע הקולי, נוצר הרושם שהסיום הזה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אפרת גוש – סוף סוף אושר</v>
+        <v>נתנאל ששון – זה רשמי</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נתנאל ששון – זה רשמי</v>
+        <v>יובל אבידן – ברוך השם אני טוב</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%aa%d7%a0%d7%90%d7%9c-%d7%a9%d7%a9%d7%95%d7%9f-%d7%96%d7%94-%d7%a8%d7%a9%d7%9e%d7%99/</v>
+        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%90%d7%91%d7%99%d7%93%d7%9f-%d7%91%d7%a8%d7%95%d7%9a-%d7%94%d7%a9%d7%9d-%d7%90%d7%a0%d7%99-%d7%98%d7%95%d7%91/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-09</v>
+        <v>2026-03-10</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>נתנאל ששון שר בלדה ים-תיכונית טיפוסית על אהבה שנגמרה, שמנסה לשלב בין הצהרה של התגברות לבין רגש שלא באמת נעלם. כבר משם השיר ברור שהדובר מבקש להכריז על סיום סופי,  אבל ככל שמתקדמים בטקסט ובביצוע הקולי, נוצר הרושם שהסיום הזה</v>
+        <v>יובל אבידן שר  שיר אמוני-אישי שמציג תהליך של חזרה פנימה וחיזוק רוחני. הוא כתוב בשפה פשוטה וישירה, עם מנגינה קליטה וקצב מיד-טמפו רגוע, ללא שיא דרמטי גדול – דבר שמשרת את המסר הפנימי והמתון של השיר. השיר מתאר תהליך של</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נתנאל ששון – זה רשמי</v>
+        <v>יובל אבידן – ברוך השם אני טוב</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>יובל אבידן – ברוך השם אני טוב</v>
+        <v>נועה פארן &amp; אביחי טוכמן – זז באדמה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%99%d7%95%d7%91%d7%9c-%d7%90%d7%91%d7%99%d7%93%d7%9f-%d7%91%d7%a8%d7%95%d7%9a-%d7%94%d7%a9%d7%9d-%d7%90%d7%a0%d7%99-%d7%98%d7%95%d7%91/</v>
+        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a4%d7%90%d7%a8%d7%9f-%d7%90%d7%91%d7%99%d7%97%d7%99-%d7%98%d7%95%d7%9b%d7%9e%d7%9f-%d7%96%d7%96-%d7%91%d7%90%d7%93%d7%9e%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-10</v>
+        <v>2026-03-11</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>יובל אבידן שר  שיר אמוני-אישי שמציג תהליך של חזרה פנימה וחיזוק רוחני. הוא כתוב בשפה פשוטה וישירה, עם מנגינה קליטה וקצב מיד-טמפו רגוע, ללא שיא דרמטי גדול – דבר שמשרת את המסר הפנימי והמתון של השיר. השיר מתאר תהליך של</v>
+        <v>השיר של נועה פארן (בביצוע) ואביחי טוכמן (יוצר/מפיק) פועל כמו ניסיון מודע ליצור מרחב קטן של חופש בתוך הרעש העירוני. זהו פופ קליט עם בסיס קצבי שמושפע מרגאטון, כמעט שיר מדיטטיבי במסווה של שיר רחבה. השיר מתאר רגע שבו המוזיקה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>יובל אבידן – ברוך השם אני טוב</v>
+        <v>נועה פארן &amp; אביחי טוכמן – זז באדמה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>נועה פארן &amp; אביחי טוכמן – זז באדמה</v>
+        <v>מיקה משה והלהקות הצבאיות – אומץ</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-11</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%a0%d7%95%d7%a2%d7%94-%d7%a4%d7%90%d7%a8%d7%9f-%d7%90%d7%91%d7%99%d7%97%d7%99-%d7%98%d7%95%d7%9b%d7%9e%d7%9f-%d7%96%d7%96-%d7%91%d7%90%d7%93%d7%9e%d7%94/</v>
+        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%9e%d7%a9%d7%94-%d7%95%d7%94%d7%9c%d7%94%d7%a7%d7%95%d7%aa-%d7%94%d7%a6%d7%91%d7%90%d7%99%d7%95%d7%aa-%d7%90%d7%95%d7%9e%d7%a5/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-11</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר של נועה פארן (בביצוע) ואביחי טוכמן (יוצר/מפיק) פועל כמו ניסיון מודע ליצור מרחב קטן של חופש בתוך הרעש העירוני. זהו פופ קליט עם בסיס קצבי שמושפע מרגאטון, כמעט שיר מדיטטיבי במסווה של שיר רחבה. השיר מתאר רגע שבו המוזיקה</v>
+        <v>השיר “אומץ” בביצוע של מיקה משה עם הלהקות הצבאיות של צה״ל הוא שיר פופ מלודי שמנסה להיות המנון עידוד לנשים בתקופת מלחמה. הוא משתמש במוזיקה רכה ומחבקת כדי להעביר מסר של כוח, עמידה ותקווה. מצד אחד הוא יעיל רגשית ופונה</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>נועה פארן &amp; אביחי טוכמן – זז באדמה</v>
+        <v>מיקה משה והלהקות הצבאיות – אומץ</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>מיקה משה והלהקות הצבאיות – אומץ</v>
+        <v>אור עמרמי ברוקמן – תמיד חוזר למנגינה</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%9e%d7%99%d7%a7%d7%94-%d7%9e%d7%a9%d7%94-%d7%95%d7%94%d7%9c%d7%94%d7%a7%d7%95%d7%aa-%d7%94%d7%a6%d7%91%d7%90%d7%99%d7%95%d7%aa-%d7%90%d7%95%d7%9e%d7%a5/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a2%d7%9e%d7%a8%d7%9e%d7%99-%d7%91%d7%a8%d7%95%d7%a7%d7%9e%d7%9f-%d7%aa%d7%9e%d7%99%d7%93-%d7%97%d7%95%d7%96%d7%a8-%d7%9c%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-11</v>
+        <v>2026-03-12</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>השיר “אומץ” בביצוע של מיקה משה עם הלהקות הצבאיות של צה״ל הוא שיר פופ מלודי שמנסה להיות המנון עידוד לנשים בתקופת מלחמה. הוא משתמש במוזיקה רכה ומחבקת כדי להעביר מסר של כוח, עמידה ותקווה. מצד אחד הוא יעיל רגשית ופונה</v>
+        <v>אור עמרמי ברוקמן שר שיר פופ שמח ופשוט לכאורה, אך בהקשר שבו נכתב – בזמן שהזמר שהה במקלטים במהלך מלחמת מלחמת שאגת הארי – הוא מקבל משמעות עמוקה יותר: המוזיקה ככלי הישרדות רגשי. השיר מתאר ניסיון לשמור על שגרה ואופטימיות</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>מיקה משה והלהקות הצבאיות – אומץ</v>
+        <v>אור עמרמי ברוקמן – תמיד חוזר למנגינה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,13 +436,13 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אור עמרמי ברוקמן – תמיד חוזר למנגינה</v>
+        <v>ג'יין בורדו – חלמתי שאתה פה</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-12</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%90%d7%95%d7%a8-%d7%a2%d7%9e%d7%a8%d7%9e%d7%99-%d7%91%d7%a8%d7%95%d7%a7%d7%9e%d7%9f-%d7%aa%d7%9e%d7%99%d7%93-%d7%97%d7%95%d7%96%d7%a8-%d7%9c%d7%9e%d7%a0%d7%92%d7%99%d7%a0%d7%94/</v>
+        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%9f-%d7%91%d7%95%d7%a8%d7%93%d7%95-%d7%97%d7%9c%d7%9e%d7%aa%d7%99-%d7%a9%d7%90%d7%aa%d7%94-%d7%a4%d7%94/</v>
       </c>
       <c r="D2" t="str">
         <v>2026-03-12</v>
@@ -451,7 +451,7 @@
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>אור עמרמי ברוקמן שר שיר פופ שמח ופשוט לכאורה, אך בהקשר שבו נכתב – בזמן שהזמר שהה במקלטים במהלך מלחמת מלחמת שאגת הארי – הוא מקבל משמעות עמוקה יותר: המוזיקה ככלי הישרדות רגשי. השיר מתאר ניסיון לשמור על שגרה ואופטימיות</v>
+        <v>דורון טלמון שרה  בלדה פולק-אקוסטית שקטה אך טעונה מאוד רגשית. היא נע בין שני צירים: חלום אישי על אדם חסר לבין אמירה דורית על צעירים שחיים בתוך מציאות של מלחמות מתמשכות. אחד האלמנטים הבולטים בו הוא ההדהוד ליצירה הקלאסית שיר</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אור עמרמי ברוקמן – תמיד חוזר למנגינה</v>
+        <v>ג'יין בורדו – חלמתי שאתה פה</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,22 +436,22 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>ג'יין בורדו – חלמתי שאתה פה</v>
+        <v>אופיר אלחייני שדה שושנים</v>
       </c>
       <c r="B2" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="C2" t="str">
-        <v>https://yosmusic.com/%d7%92%d7%99%d7%99%d7%9f-%d7%91%d7%95%d7%a8%d7%93%d7%95-%d7%97%d7%9c%d7%9e%d7%aa%d7%99-%d7%a9%d7%90%d7%aa%d7%94-%d7%a4%d7%94/</v>
+        <v>https://yosmusic.com/%d7%90%d7%95%d7%a4%d7%99%d7%a8-%d7%90%d7%9c%d7%97%d7%99%d7%99%d7%a0%d7%99-%d7%a9%d7%93%d7%94-%d7%a9%d7%95%d7%a9%d7%a0%d7%99%d7%9d/</v>
       </c>
       <c r="D2" t="str">
-        <v>2026-03-12</v>
+        <v>2026-03-14</v>
       </c>
       <c r="E2" t="str">
         <v/>
       </c>
       <c r="F2" t="str">
-        <v>דורון טלמון שרה  בלדה פולק-אקוסטית שקטה אך טעונה מאוד רגשית. היא נע בין שני צירים: חלום אישי על אדם חסר לבין אמירה דורית על צעירים שחיים בתוך מציאות של מלחמות מתמשכות. אחד האלמנטים הבולטים בו הוא ההדהוד ליצירה הקלאסית שיר</v>
+        <v>השיר ששר אופיר אלחייני נכתב על רקע הטראומה של מתקפת חמאס על ישראל ב־7 באוקטובר 2023, ובמרכזו עומד דיסוננס בין יופי טבעי לבין הרס אנושי. השיר משתמש בדימויים תנ"כיים, קבליים ופיוטיים כדי לעבד כאב לאומי ולהפוך אותו לתקווה רוחנית. אלחייני</v>
       </c>
       <c r="G2" t="str">
         <v/>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>ג'יין בורדו – חלמתי שאתה פה</v>
+        <v>אופיר אלחייני שדה שושנים</v>
       </c>
     </row>
   </sheetData>

--- a/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
+++ b/data/tags/סינגלים חדשים/sites/yosmusic-singles/2026-03-week02/titles.xlsx
@@ -436,7 +436,7 @@
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>אופיר אלחייני שדה שושנים</v>
+        <v>אופיר אלחייני – שדה שושנים</v>
       </c>
       <c r="B2" t="str">
         <v>2026-03-14</v>
@@ -469,7 +469,7 @@
         <v/>
       </c>
       <c r="L2" t="str">
-        <v>אופיר אלחייני שדה שושנים</v>
+        <v>אופיר אלחייני – שדה שושנים</v>
       </c>
     </row>
   </sheetData>
